--- a/Encollect_Web_SCB_P1/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/Encollect_Web_SCB_P1/Cypress/fixtures/AgencyTemplate.xlsx
@@ -401,61 +401,61 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Liam</v>
+        <v>Name</v>
       </c>
       <c r="B2" t="str">
-        <v>Altenwerth</v>
+        <v>Hackett</v>
       </c>
       <c r="C2" t="str">
-        <v>0JXV9H</v>
+        <v>62FXVF</v>
       </c>
       <c r="D2" t="str">
-        <v>Francisco11@yahoo.com</v>
+        <v>Susie.Kerluke@yahoo.com</v>
       </c>
       <c r="E2" t="str">
-        <v>ukDBSXHQ</v>
+        <v>w0EhiPQu</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-03-29</v>
+        <v>2024-11-29</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-08-22</v>
+        <v>2025-07-09</v>
       </c>
       <c r="H2" t="str">
-        <v>J81RjPGa5X</v>
+        <v>Hvr6fyGdab</v>
       </c>
       <c r="I2" t="str">
-        <v>Computers</v>
+        <v>Industrial</v>
       </c>
       <c r="J2" t="str">
-        <v>Future Division Executive</v>
+        <v>Investor Assurance Planner</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-01-18</v>
+        <v>2024-11-29</v>
       </c>
       <c r="L2" t="str">
-        <v>8614275080</v>
+        <v>8133146919</v>
       </c>
       <c r="M2" t="str">
-        <v>Estella85@yahoo.com</v>
+        <v>Erna_Hand@gmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Estell</v>
+        <v>Mariano</v>
       </c>
       <c r="O2" t="str">
-        <v>34478 Broadway Avenue</v>
+        <v>831 Mavis Mews</v>
       </c>
       <c r="P2" t="str">
-        <v>92111</v>
+        <v>72469</v>
       </c>
       <c r="Q2" t="str">
-        <v>2024-10-29</v>
+        <v>2025-10-04</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-08-29</v>
+        <v>2025-07-13</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-30</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P1/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/Encollect_Web_SCB_P1/Cypress/fixtures/AgencyTemplate.xlsx
@@ -401,61 +401,61 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Veda</v>
+        <v>Maggie</v>
       </c>
       <c r="B2" t="str">
-        <v>Towne</v>
+        <v>Harris</v>
       </c>
       <c r="C2" t="str">
-        <v>33U20M</v>
+        <v>WQG3KM</v>
       </c>
       <c r="D2" t="str">
-        <v>Annalise82@gmail.com</v>
+        <v>Kian_Friesen1@gmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>a0fZ1ew9</v>
+        <v>Q7DCD5mf</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-05-29</v>
+        <v>2026-02-10</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-12-21</v>
+        <v>2025-07-13</v>
       </c>
       <c r="H2" t="str">
-        <v>ZoYvVJZVMS</v>
+        <v>XwyHgEcizo</v>
       </c>
       <c r="I2" t="str">
-        <v>Kids</v>
+        <v>Sports</v>
       </c>
       <c r="J2" t="str">
-        <v>Regional Assurance Officer</v>
+        <v>National Marketing Technician</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-06-27</v>
+        <v>2026-01-12</v>
       </c>
       <c r="L2" t="str">
-        <v>0124392015</v>
+        <v>8604723173</v>
       </c>
       <c r="M2" t="str">
-        <v>Morris_Boehm27@gmail.com</v>
+        <v>Abdullah.Reilly97@hotmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Gene</v>
+        <v>Krystina</v>
       </c>
       <c r="O2" t="str">
-        <v>88611 S Washington Avenue</v>
+        <v>37349 Douglas Points</v>
       </c>
       <c r="P2" t="str">
-        <v>67747</v>
+        <v>81413</v>
       </c>
       <c r="Q2" t="str">
-        <v>2025-05-09</v>
+        <v>2025-12-13</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-02-14</v>
+        <v>2025-12-15</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-12-20</v>
+        <v>2026-04-09</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P1/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/Encollect_Web_SCB_P1/Cypress/fixtures/AgencyTemplate.xlsx
@@ -401,61 +401,61 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Maggie</v>
+        <v>Zita</v>
       </c>
       <c r="B2" t="str">
-        <v>Harris</v>
+        <v>O'Kon</v>
       </c>
       <c r="C2" t="str">
-        <v>WQG3KM</v>
+        <v>JSPP9E</v>
       </c>
       <c r="D2" t="str">
-        <v>Kian_Friesen1@gmail.com</v>
+        <v>Jedidiah_Gulgowski1@yahoo.com</v>
       </c>
       <c r="E2" t="str">
-        <v>Q7DCD5mf</v>
+        <v>kcmaqBk4</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-02-10</v>
+        <v>2026-04-13</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-07-13</v>
+        <v>2026-02-27</v>
       </c>
       <c r="H2" t="str">
-        <v>XwyHgEcizo</v>
+        <v>0hQVvzwMfw</v>
       </c>
       <c r="I2" t="str">
-        <v>Sports</v>
+        <v>Automotive</v>
       </c>
       <c r="J2" t="str">
-        <v>National Marketing Technician</v>
+        <v>Product Accounts Director</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-01-12</v>
+        <v>2026-02-28</v>
       </c>
       <c r="L2" t="str">
-        <v>8604723173</v>
+        <v>9290704331</v>
       </c>
       <c r="M2" t="str">
-        <v>Abdullah.Reilly97@hotmail.com</v>
+        <v>Jade70@hotmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Krystina</v>
+        <v>Layne</v>
       </c>
       <c r="O2" t="str">
-        <v>37349 Douglas Points</v>
+        <v>68629 County Line Road</v>
       </c>
       <c r="P2" t="str">
-        <v>81413</v>
+        <v>70658</v>
       </c>
       <c r="Q2" t="str">
-        <v>2025-12-13</v>
+        <v>2026-01-20</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-12-15</v>
+        <v>2026-03-08</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-07-06</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P1/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/Encollect_Web_SCB_P1/Cypress/fixtures/AgencyTemplate.xlsx
@@ -401,61 +401,61 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Zita</v>
+        <v>Lilyan</v>
       </c>
       <c r="B2" t="str">
-        <v>O'Kon</v>
+        <v>Jones</v>
       </c>
       <c r="C2" t="str">
-        <v>JSPP9E</v>
+        <v>YSAQZD</v>
       </c>
       <c r="D2" t="str">
-        <v>Jedidiah_Gulgowski1@yahoo.com</v>
+        <v>Kristy_Wolf@hotmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>kcmaqBk4</v>
+        <v>5YUb5Y1i</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-04-13</v>
+        <v>2025-09-28</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-02-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="H2" t="str">
-        <v>0hQVvzwMfw</v>
+        <v>vvsztZmq32</v>
       </c>
       <c r="I2" t="str">
-        <v>Automotive</v>
+        <v>Jewelry</v>
       </c>
       <c r="J2" t="str">
-        <v>Product Accounts Director</v>
+        <v>Dynamic Group Specialist</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-02-28</v>
+        <v>2025-06-02</v>
       </c>
       <c r="L2" t="str">
-        <v>9290704331</v>
+        <v>7051413052</v>
       </c>
       <c r="M2" t="str">
-        <v>Jade70@hotmail.com</v>
+        <v>Cecelia88@yahoo.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Layne</v>
+        <v>Hobart</v>
       </c>
       <c r="O2" t="str">
-        <v>68629 County Line Road</v>
+        <v>5815 Vincent Causeway</v>
       </c>
       <c r="P2" t="str">
-        <v>70658</v>
+        <v>39978</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-01-20</v>
+        <v>2026-03-15</v>
       </c>
       <c r="R2" t="str">
-        <v>2026-03-08</v>
+        <v>2025-10-05</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-07-06</v>
+        <v>2026-11-05</v>
       </c>
     </row>
   </sheetData>
